--- a/inst/extdata/Tutorial/Scenarios.xlsx
+++ b/inst/extdata/Tutorial/Scenarios.xlsx
@@ -103,7 +103,7 @@
     <t xml:space="preserve">I123413</t>
   </si>
   <si>
-    <t xml:space="preserve">iv 1 mg 5 min.pkml</t>
+    <t xml:space="preserve">iv_1_mg_5_min.pkml</t>
   </si>
   <si>
     <t xml:space="preserve">virtual_twin_population</t>
@@ -118,7 +118,7 @@
     <t xml:space="preserve">random_population</t>
   </si>
   <si>
-    <t xml:space="preserve">po 3 mg solution.pkml</t>
+    <t xml:space="preserve">po_3_mg_solution.pkml</t>
   </si>
   <si>
     <t xml:space="preserve">random_population_po</t>
@@ -191,7 +191,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +221,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -285,7 +291,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -298,11 +304,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -576,7 +586,7 @@
       <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -584,7 +594,7 @@
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="1" t="n">
@@ -598,13 +608,13 @@
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -633,10 +643,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -688,10 +698,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>30</v>
       </c>
     </row>

--- a/inst/extdata/Tutorial/Scenarios.xlsx
+++ b/inst/extdata/Tutorial/Scenarios.xlsx
@@ -112,16 +112,16 @@
     <t xml:space="preserve">study_1234_population</t>
   </si>
   <si>
+    <t xml:space="preserve">random_population_po</t>
+  </si>
+  <si>
+    <t xml:space="preserve">random_population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">po_3_mg_solution.pkml</t>
+  </si>
+  <si>
     <t xml:space="preserve">random_population_iv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">random_population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">po_3_mg_solution.pkml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">random_population_po</t>
   </si>
   <si>
     <t xml:space="preserve">OutputPathId</t>
@@ -191,7 +191,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,12 +221,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -291,7 +285,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -304,15 +298,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -594,7 +584,7 @@
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="1" t="n">
@@ -608,7 +598,7 @@
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="1" t="n">
@@ -643,10 +633,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -698,10 +688,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
